--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF5DE0E1-8C35-4911-B46E-A2A6B9F0F4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59E5508A-F2D9-43B6-858D-3A2EA9C9A8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5198C5FE-D2C0-4604-B0F0-A73A4DCC64BB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{03E79A6B-CA65-4047-9BE3-4DAE65C9770A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4801,7 +4801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB385CD-50F9-4D0D-A090-CEA8E223BD36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B594077-D137-4927-9624-7918D9446206}">
   <dimension ref="B3:L699"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59E5508A-F2D9-43B6-858D-3A2EA9C9A8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29DF268A-066F-4A5A-93E2-8E8F999F0E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{03E79A6B-CA65-4047-9BE3-4DAE65C9770A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DC662BD2-D40F-4957-B282-0B10017F3715}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4801,7 +4801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B594077-D137-4927-9624-7918D9446206}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D678C4A-6B9A-4A05-8014-9634D8E8A70B}">
   <dimension ref="B3:L699"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29DF268A-066F-4A5A-93E2-8E8F999F0E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C342F72-927E-4659-A9A9-710FE5511E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DC662BD2-D40F-4957-B282-0B10017F3715}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{45F6DD4C-0A0C-4EE1-84E2-373A39B9D217}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4801,7 +4801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D678C4A-6B9A-4A05-8014-9634D8E8A70B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4340EAFE-B4C9-4FBB-920C-1484310BE9EC}">
   <dimension ref="B3:L699"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4710B43-2762-479F-B4C8-288C5B23DDAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CAE02A0-8CD6-48BA-BE72-578EC27E318B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3ACAC754-2758-45E6-935C-F8C99EDAF5CC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1B4A2890-F2B4-46F1-B111-A87E25E40D71}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B37F6C7-3980-42FF-9DA6-01700BA955F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E98546C-C4A7-4707-97F6-C71F99E7FEED}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CAE02A0-8CD6-48BA-BE72-578EC27E318B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C418E45-A3E9-4B11-B8D9-60890773FB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1B4A2890-F2B4-46F1-B111-A87E25E40D71}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AC3286DC-B266-4327-B1B6-923A107F3366}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E98546C-C4A7-4707-97F6-C71F99E7FEED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83156541-38E1-4D92-8211-2943C26AA8E3}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C418E45-A3E9-4B11-B8D9-60890773FB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD96814B-3365-443C-9660-5C77825947FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AC3286DC-B266-4327-B1B6-923A107F3366}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{324B7FF1-2FBB-443C-B0DB-22CF0F7701EF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83156541-38E1-4D92-8211-2943C26AA8E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77D98A7-6FF4-4791-BBBB-0E66D04EA039}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD96814B-3365-443C-9660-5C77825947FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{600ED3F6-4F6D-4637-BFE8-A4B09B2E768A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{324B7FF1-2FBB-443C-B0DB-22CF0F7701EF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4D1B319D-7035-4EAC-8354-D12BDB10F782}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77D98A7-6FF4-4791-BBBB-0E66D04EA039}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C8FF78-2D93-4E1D-B176-E88EE6824B89}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{600ED3F6-4F6D-4637-BFE8-A4B09B2E768A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C04CD25A-2B2A-49BC-8A3B-9D2A95758EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4D1B319D-7035-4EAC-8354-D12BDB10F782}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B83C0BFE-96A4-4FD1-9861-E0156577A1E1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C8FF78-2D93-4E1D-B176-E88EE6824B89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10386A18-1CB0-45B5-8197-FE36F746726B}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C04CD25A-2B2A-49BC-8A3B-9D2A95758EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6034A814-29B1-44E2-9E37-ED1DE631A6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B83C0BFE-96A4-4FD1-9861-E0156577A1E1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4B193DB3-8DAD-4844-BF33-9B6DB4ED3B92}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10386A18-1CB0-45B5-8197-FE36F746726B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491F0C91-6E40-48FB-AC10-3842D5746523}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6034A814-29B1-44E2-9E37-ED1DE631A6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43F57B41-E35E-4072-A673-11F96C43B1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4B193DB3-8DAD-4844-BF33-9B6DB4ED3B92}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{625A9AAD-080D-47F8-BAC0-52CE7AB8C161}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491F0C91-6E40-48FB-AC10-3842D5746523}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E902956-ADEB-47A2-A6B6-E7EE9C76E548}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43F57B41-E35E-4072-A673-11F96C43B1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AA2A56F-6051-4615-A8BD-1D40C30803C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{625A9AAD-080D-47F8-BAC0-52CE7AB8C161}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ACFF9BCA-AF15-4A6A-82FB-94DEAA975944}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E902956-ADEB-47A2-A6B6-E7EE9C76E548}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD725E4-667A-4339-BDF9-DD71007258A8}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AA2A56F-6051-4615-A8BD-1D40C30803C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47B3252F-91DD-47E3-A098-80ABAEDBF889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ACFF9BCA-AF15-4A6A-82FB-94DEAA975944}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E0A9712D-6F78-4993-B869-261D1F825FA4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD725E4-667A-4339-BDF9-DD71007258A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F9E86EB-15E0-4463-AD57-FA82F6F8B322}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47B3252F-91DD-47E3-A098-80ABAEDBF889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68E44D9E-E7BA-4AF8-9349-9C655D5984CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E0A9712D-6F78-4993-B869-261D1F825FA4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F1E119C7-D08C-4139-AA0E-07200B8FDEFC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F9E86EB-15E0-4463-AD57-FA82F6F8B322}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F9256B-27AE-41F2-9F8D-9610CEA807F0}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68E44D9E-E7BA-4AF8-9349-9C655D5984CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5193BC0-C984-491F-8FBC-AB087116685F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F1E119C7-D08C-4139-AA0E-07200B8FDEFC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{857DBE33-01FD-4998-9524-1EE597D35B43}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F9256B-27AE-41F2-9F8D-9610CEA807F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97FDC60-FF65-4BEE-AB69-5ED2FA006E4A}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5193BC0-C984-491F-8FBC-AB087116685F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEA5F040-1B61-41FB-8920-66DF33EBDEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{857DBE33-01FD-4998-9524-1EE597D35B43}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B24DC100-C8CB-48A4-B9EA-9ED07B4A6677}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97FDC60-FF65-4BEE-AB69-5ED2FA006E4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE0D8158-31E5-4658-9340-11B607D5059A}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEA5F040-1B61-41FB-8920-66DF33EBDEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51463B30-A766-4294-B123-A981CEE0E3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B24DC100-C8CB-48A4-B9EA-9ED07B4A6677}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F884153F-7028-4EE8-A709-82523511EFA4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE0D8158-31E5-4658-9340-11B607D5059A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FEF2E1-1CC9-4B0A-B54E-CD1C2F960682}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51463B30-A766-4294-B123-A981CEE0E3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6DE6076-E55B-4799-BE7F-5417C51EACFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F884153F-7028-4EE8-A709-82523511EFA4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{57ADF1F9-9E91-49C7-82B8-C40CAFDD2AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FEF2E1-1CC9-4B0A-B54E-CD1C2F960682}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7DF3405-C72F-4D57-8F7C-500BFC608362}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6DE6076-E55B-4799-BE7F-5417C51EACFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6947A00E-69F3-42F6-83C0-DC8141AB5D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{57ADF1F9-9E91-49C7-82B8-C40CAFDD2AEA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DE4B73BB-270B-4982-B95C-BA4E71896501}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7DF3405-C72F-4D57-8F7C-500BFC608362}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294F48DD-483F-4EF8-B786-BAAEC1739AF8}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6947A00E-69F3-42F6-83C0-DC8141AB5D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D136846-D04D-4D21-8679-AF4189E014C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DE4B73BB-270B-4982-B95C-BA4E71896501}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{55674301-13B4-4188-B8D3-75A08B91CCB6}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294F48DD-483F-4EF8-B786-BAAEC1739AF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E790D8C-2E22-49F0-9229-3B18C7FDC147}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D136846-D04D-4D21-8679-AF4189E014C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8B02FCF-8414-4E27-A517-0EBA1A803D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{55674301-13B4-4188-B8D3-75A08B91CCB6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2CAD31F9-A95F-46E4-BCC8-598EA70DD5DD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E790D8C-2E22-49F0-9229-3B18C7FDC147}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0443CDB2-9B07-4CA3-AB86-A309AFA0F3E3}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8B02FCF-8414-4E27-A517-0EBA1A803D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E194C55-7E30-4012-8AAA-49327BDF410C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2CAD31F9-A95F-46E4-BCC8-598EA70DD5DD}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{A0E69C9A-A952-412C-B6AC-344EAED1D151}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0443CDB2-9B07-4CA3-AB86-A309AFA0F3E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B604E8-23A1-416E-A4CD-DB8EC87A7677}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E194C55-7E30-4012-8AAA-49327BDF410C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29ED04D3-9ECD-4806-9A86-CF3EDD59BE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{A0E69C9A-A952-412C-B6AC-344EAED1D151}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" xr2:uid="{32D0CF59-CD85-43EE-8299-ECD82C148ADD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B604E8-23A1-416E-A4CD-DB8EC87A7677}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382A1A9C-F17C-4187-AD7A-3832BA589942}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29ED04D3-9ECD-4806-9A86-CF3EDD59BE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E2D87F-54ED-4421-A9B5-A5B9707BEB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" xr2:uid="{32D0CF59-CD85-43EE-8299-ECD82C148ADD}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{7A89E58C-DE01-4CE9-A3E4-DCCA97B24C9E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382A1A9C-F17C-4187-AD7A-3832BA589942}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0815BFB9-29C5-4955-BC6E-016C1173877F}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E2D87F-54ED-4421-A9B5-A5B9707BEB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FAF2878-DE51-44D5-85A4-87C627CC6D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{7A89E58C-DE01-4CE9-A3E4-DCCA97B24C9E}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{24592CD6-EFED-419D-B730-F40A8F41EB69}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0815BFB9-29C5-4955-BC6E-016C1173877F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EEFB1C1-EB20-4C50-8054-47FAA68C6B6B}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FAF2878-DE51-44D5-85A4-87C627CC6D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B83D0CF-6079-4435-977D-AD6770B9C32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{24592CD6-EFED-419D-B730-F40A8F41EB69}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{C046C367-86A3-44CC-8E22-8D94F2C94B05}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EEFB1C1-EB20-4C50-8054-47FAA68C6B6B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038F2669-FB3D-48F7-B23D-71AC99E13441}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B83D0CF-6079-4435-977D-AD6770B9C32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87463DB0-E74C-4A9B-9CCF-108C6F5D5430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{C046C367-86A3-44CC-8E22-8D94F2C94B05}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{75718132-F6B0-4A9C-9C89-10EC91A9F34B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038F2669-FB3D-48F7-B23D-71AC99E13441}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D61BBD7-884C-4A73-998D-605958C25E6F}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87463DB0-E74C-4A9B-9CCF-108C6F5D5430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98B565AB-ED18-45AD-9AE9-8B7406A2CF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{75718132-F6B0-4A9C-9C89-10EC91A9F34B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C9340AB6-24DD-4B33-8BB9-46FA8E145C65}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D61BBD7-884C-4A73-998D-605958C25E6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9095DD2D-8D24-4768-8B87-445A1E0F85E2}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98B565AB-ED18-45AD-9AE9-8B7406A2CF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77A561B0-FB5D-4C1B-BCD0-A4356E6FD8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C9340AB6-24DD-4B33-8BB9-46FA8E145C65}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8095F0A6-E861-40FD-961F-E5FC324CA9A4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9095DD2D-8D24-4768-8B87-445A1E0F85E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA3A256-FF1A-44D9-ACFD-E200F479C4E2}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77A561B0-FB5D-4C1B-BCD0-A4356E6FD8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A797F41D-D8E6-428E-9328-C9C881BC4784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8095F0A6-E861-40FD-961F-E5FC324CA9A4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ACFF5B03-A42E-40C9-A60F-E6CD2A9A5084}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA3A256-FF1A-44D9-ACFD-E200F479C4E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6E41B0-6959-47FD-BF6F-17B2FEFC1E75}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A797F41D-D8E6-428E-9328-C9C881BC4784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B82FA2B9-9965-4E80-8165-8BFD3FA11F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ACFF5B03-A42E-40C9-A60F-E6CD2A9A5084}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3B6822D-DAD0-4A16-81BC-3D91862C5F9E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6E41B0-6959-47FD-BF6F-17B2FEFC1E75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04613F6D-9E35-4A75-8A6B-8444B4E7B56F}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B82FA2B9-9965-4E80-8165-8BFD3FA11F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96739C38-D30A-4F73-BF4A-5995EFA3046E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3B6822D-DAD0-4A16-81BC-3D91862C5F9E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{809D4836-0F0C-4C56-AA4A-1923501D0AB8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04613F6D-9E35-4A75-8A6B-8444B4E7B56F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FA03519-40CE-4DA4-865F-D1B0BA085ED0}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96739C38-D30A-4F73-BF4A-5995EFA3046E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E840B65-08D8-46D4-966D-4F4811D012DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{809D4836-0F0C-4C56-AA4A-1923501D0AB8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DD94A710-BE7A-4569-876C-003F6FCF6CE4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FA03519-40CE-4DA4-865F-D1B0BA085ED0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCE1C88-A5D2-4F71-B798-76B824F996E3}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E840B65-08D8-46D4-966D-4F4811D012DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{844A3436-6A88-4522-A357-CAAE0F0B28B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DD94A710-BE7A-4569-876C-003F6FCF6CE4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F048DD97-0DF3-4505-9CA3-38A662D24645}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCE1C88-A5D2-4F71-B798-76B824F996E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA80856-5F52-4C31-AD4B-F8A3B57DB79E}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{844A3436-6A88-4522-A357-CAAE0F0B28B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15479B53-762C-43C6-AFAC-ACD929A4DDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F048DD97-0DF3-4505-9CA3-38A662D24645}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CF3410D6-A8B9-454F-A902-2E4B4FC385D2}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA80856-5F52-4C31-AD4B-F8A3B57DB79E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20048BBD-C0D7-4E40-8A3B-3E91EEA9BA75}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15479B53-762C-43C6-AFAC-ACD929A4DDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3FB3511-740F-4CBA-A233-6E3DA7EBF2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CF3410D6-A8B9-454F-A902-2E4B4FC385D2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6EF9C4F3-C252-4322-B89B-0F72C5C2DBD5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20048BBD-C0D7-4E40-8A3B-3E91EEA9BA75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFD9D30-8DBF-4B22-BD96-64A0C15C5533}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3FB3511-740F-4CBA-A233-6E3DA7EBF2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C9E6E3-523B-4AE6-8A7C-D8DA4AFD84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6EF9C4F3-C252-4322-B89B-0F72C5C2DBD5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D5675EBC-EED2-47F7-A33A-8E0901CA12F0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFD9D30-8DBF-4B22-BD96-64A0C15C5533}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83952014-F65B-4963-850B-08F9D86B55A0}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C9E6E3-523B-4AE6-8A7C-D8DA4AFD84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28DC0F0D-18B3-44A8-85AF-A08C558CBC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D5675EBC-EED2-47F7-A33A-8E0901CA12F0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4D92FBEE-51D3-44F4-A5A7-A6B166B1FA3C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83952014-F65B-4963-850B-08F9D86B55A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F3DFC94-4E4B-4739-8F48-9C57729D2D69}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28DC0F0D-18B3-44A8-85AF-A08C558CBC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD97D3E3-9AA8-4A53-AB1B-5D53141D7A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4D92FBEE-51D3-44F4-A5A7-A6B166B1FA3C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2D73AA05-07C5-430D-91AC-D207120FF6E4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F3DFC94-4E4B-4739-8F48-9C57729D2D69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B506F0-EA66-401B-B2AC-652C1BFC75EA}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD97D3E3-9AA8-4A53-AB1B-5D53141D7A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D97F06B-5810-4A85-975E-9416472455FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2D73AA05-07C5-430D-91AC-D207120FF6E4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9DF33EE0-F843-4255-9462-A0D2B22C1FB5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B506F0-EA66-401B-B2AC-652C1BFC75EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BDDED3-39C8-4F8D-9FFF-012AC9AA6164}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D97F06B-5810-4A85-975E-9416472455FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91D18A13-C9E5-4CD8-AB53-B39708933C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9DF33EE0-F843-4255-9462-A0D2B22C1FB5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{855DEADA-0AED-46FD-9B0B-56D5662BE94B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BDDED3-39C8-4F8D-9FFF-012AC9AA6164}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F86C0C-17FE-4B71-9467-2E5943CE0A9D}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91D18A13-C9E5-4CD8-AB53-B39708933C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41E0DBBE-3579-4CD6-81FC-E12F56A87D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{855DEADA-0AED-46FD-9B0B-56D5662BE94B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{574E4C4E-A3ED-4657-94F0-FEDA7AE69F9F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F86C0C-17FE-4B71-9467-2E5943CE0A9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{891C4912-3C86-41AB-ABFD-551319ED9A73}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41E0DBBE-3579-4CD6-81FC-E12F56A87D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A11091C-A751-407D-8F0C-F6B581750008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{574E4C4E-A3ED-4657-94F0-FEDA7AE69F9F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{32D31893-6A54-43E0-81FA-D64930767C71}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{891C4912-3C86-41AB-ABFD-551319ED9A73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B020D885-50F0-4C8F-A82B-EF8C1D472E62}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A11091C-A751-407D-8F0C-F6B581750008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA3C296A-A836-45B5-8DD1-CDFD5905156F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{32D31893-6A54-43E0-81FA-D64930767C71}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6AF8CDB8-1FE7-4851-B2CE-E15E67D00F4E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B020D885-50F0-4C8F-A82B-EF8C1D472E62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{455F830F-3771-44CB-B8C7-3AE557CFD987}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA3C296A-A836-45B5-8DD1-CDFD5905156F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3C7589A-5728-4EA0-9F46-5AE8004E7CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6AF8CDB8-1FE7-4851-B2CE-E15E67D00F4E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97EB084F-85EB-4D4C-BD5B-C3143B4F5437}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{455F830F-3771-44CB-B8C7-3AE557CFD987}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21BFCD86-4AD6-4E49-89A3-E67CA9C36AF4}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3C7589A-5728-4EA0-9F46-5AE8004E7CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{023E765B-06AA-4582-927A-CFF610CE171F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97EB084F-85EB-4D4C-BD5B-C3143B4F5437}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F586102-61AE-4762-A5A9-C2D19EC1921C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21BFCD86-4AD6-4E49-89A3-E67CA9C36AF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFBA3F14-A259-4B78-974C-1F3180EDD2ED}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{023E765B-06AA-4582-927A-CFF610CE171F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{393AB827-61A6-4620-9AFD-6D83FF52347D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F586102-61AE-4762-A5A9-C2D19EC1921C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A0E0907A-7574-4BEE-8134-DF1F618A3D15}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFBA3F14-A259-4B78-974C-1F3180EDD2ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D1E890-F028-49E2-B3D5-0138A72054C5}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{393AB827-61A6-4620-9AFD-6D83FF52347D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2131E588-5592-49EE-A67D-0F01C62B26CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A0E0907A-7574-4BEE-8134-DF1F618A3D15}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DEDA4B48-806A-4DC7-8A3E-D99491F224E8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D1E890-F028-49E2-B3D5-0138A72054C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99121C0-041C-467B-BCF6-7E769D9D4DA0}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2131E588-5592-49EE-A67D-0F01C62B26CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8C6C716-C621-44BF-9D4A-A94889280DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DEDA4B48-806A-4DC7-8A3E-D99491F224E8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D7DCF9EE-EF4D-47B9-88FE-D34B15AFFCFF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99121C0-041C-467B-BCF6-7E769D9D4DA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C439D1-8955-43C1-8E99-F530BBCFF043}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8C6C716-C621-44BF-9D4A-A94889280DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8998298-712C-41B9-B2D4-291D6BA6FADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D7DCF9EE-EF4D-47B9-88FE-D34B15AFFCFF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F0729A4F-0BFC-4B64-8896-1ADFC4D8B1A4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C439D1-8955-43C1-8E99-F530BBCFF043}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7B385E-789A-4C15-8186-9AF75BFB4C59}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8998298-712C-41B9-B2D4-291D6BA6FADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B0DBDE5-2E84-4170-B39A-CABC2C74BC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F0729A4F-0BFC-4B64-8896-1ADFC4D8B1A4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0E7BFE8E-6134-4E4A-BF4F-F4EFF07D2323}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7B385E-789A-4C15-8186-9AF75BFB4C59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048AB29E-8CBB-4B3E-9A21-BAD0C11A4190}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B0DBDE5-2E84-4170-B39A-CABC2C74BC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F251524-2318-407F-B590-0172C69ABD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0E7BFE8E-6134-4E4A-BF4F-F4EFF07D2323}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0A3D9918-30C3-4B9B-9540-F525A94682AF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048AB29E-8CBB-4B3E-9A21-BAD0C11A4190}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155F790D-4E73-4286-9ABB-D45EC87B37F1}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F251524-2318-407F-B590-0172C69ABD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E35713-71F6-4E78-B740-26E928D48A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0A3D9918-30C3-4B9B-9540-F525A94682AF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B962AED0-699D-416C-9325-AF495B2B2CDF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155F790D-4E73-4286-9ABB-D45EC87B37F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C104AC86-3B17-445C-B63E-86B8CCDF9553}">
   <dimension ref="B3:L319"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
